--- a/data/hex_xlsx/SANOMA.HE.xlsx
+++ b/data/hex_xlsx/SANOMA.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="551">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1068,7 +1068,7 @@
     <t>Other Interest-Bearing Liabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">Financial liabilities </t>
+    <t>Financial liabilities not use</t>
   </si>
   <si>
     <t>Financial Liabilities - Short-Term - Balancing value</t>
@@ -1096,6 +1096,9 @@
   </si>
   <si>
     <t>Pension obligations</t>
+  </si>
+  <si>
+    <t>Financial liabilities LT</t>
   </si>
   <si>
     <t>Finance Lease Liabilities</t>
@@ -19264,8 +19267,8 @@
       </c>
     </row>
     <row r="155" ht="15.0" customHeight="1">
-      <c r="A155" s="14" t="s">
-        <v>344</v>
+      <c r="A155" s="24" t="s">
+        <v>359</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -19353,7 +19356,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -19406,7 +19409,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -19479,8 +19482,8 @@
       <c r="W159" s="15"/>
     </row>
     <row r="160" ht="15.0" customHeight="1">
-      <c r="A160" s="14" t="s">
-        <v>344</v>
+      <c r="A160" s="24" t="s">
+        <v>359</v>
       </c>
       <c r="B160" s="16">
         <v>4248.32</v>
@@ -19520,8 +19523,8 @@
       <c r="W160" s="15"/>
     </row>
     <row r="161" ht="15.0" customHeight="1">
-      <c r="A161" s="14" t="s">
-        <v>344</v>
+      <c r="A161" s="24" t="s">
+        <v>359</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="16">
@@ -19627,7 +19630,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="15">
@@ -19692,7 +19695,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B164" s="15"/>
       <c r="C164" s="22">
@@ -19721,7 +19724,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B165" s="22">
         <v>27.17</v>
@@ -19843,7 +19846,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B167" s="15"/>
       <c r="C167" s="22">
@@ -19874,7 +19877,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -19915,7 +19918,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="22">
@@ -19978,7 +19981,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -20011,7 +20014,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -20044,7 +20047,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -20141,7 +20144,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -20231,7 +20234,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B177" s="19">
         <v>6229.53</v>
@@ -20302,7 +20305,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -20343,7 +20346,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B179" s="21">
         <v>-1.18</v>
@@ -20398,7 +20401,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B180" s="18">
         <v>11796.29</v>
@@ -20469,7 +20472,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B181" s="16">
         <v>842.34</v>
@@ -20540,7 +20543,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B182" s="21">
         <v>-80.34</v>
@@ -20597,7 +20600,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B183" s="16">
         <v>2478.58</v>
@@ -20660,7 +20663,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B184" s="15"/>
       <c r="C184" s="20">
@@ -20727,7 +20730,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B185" s="15"/>
       <c r="C185" s="16">
@@ -20794,7 +20797,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B186" s="16">
         <v>3623.36</v>
@@ -20825,7 +20828,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -20864,7 +20867,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B188" s="16">
         <v>1761.47</v>
@@ -20934,7 +20937,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -20971,7 +20974,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -21008,7 +21011,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -21045,7 +21048,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B193" s="19">
         <v>8625.41</v>
@@ -21187,7 +21190,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B195" s="27">
         <v>11.81</v>
@@ -21258,7 +21261,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B196" s="21">
         <v>-2.36</v>
@@ -21293,7 +21296,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B197" s="19">
         <v>8634.86</v>
@@ -21364,7 +21367,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -21405,7 +21408,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B199" s="18">
         <v>20431.14</v>
@@ -21476,7 +21479,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B200" s="16">
         <v>162.77</v>
@@ -21547,7 +21550,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B201" s="22">
         <v>0.79</v>
@@ -21618,7 +21621,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B202" s="16">
         <v>163.57</v>
@@ -21689,7 +21692,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -21746,7 +21749,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -21783,7 +21786,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -21816,7 +21819,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="16">
@@ -21875,7 +21878,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B207" s="15"/>
       <c r="C207" s="16">
@@ -21918,7 +21921,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B208" s="15"/>
       <c r="C208" s="16">
@@ -21961,7 +21964,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="16">
@@ -22004,7 +22007,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B210" s="15"/>
       <c r="C210" s="22">
@@ -22063,7 +22066,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B211" s="15"/>
       <c r="C211" s="16">
@@ -22122,7 +22125,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -22177,7 +22180,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -22218,7 +22221,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -22251,7 +22254,7 @@
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -22294,7 +22297,7 @@
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B216" s="15"/>
       <c r="C216" s="16">
@@ -22347,7 +22350,7 @@
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B217" s="15"/>
       <c r="C217" s="16">
@@ -22402,7 +22405,7 @@
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B218" s="15"/>
       <c r="C218" s="16">
@@ -22461,7 +22464,7 @@
     </row>
     <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -22494,7 +22497,7 @@
     </row>
     <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -22527,7 +22530,7 @@
     </row>
     <row r="221" ht="15.0" customHeight="1">
       <c r="A221" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B221" s="15"/>
       <c r="C221" s="16">
@@ -22564,7 +22567,7 @@
     </row>
     <row r="222" ht="15.0" customHeight="1">
       <c r="A222" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -22597,7 +22600,7 @@
     </row>
     <row r="223" ht="15.0" customHeight="1">
       <c r="A223" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -22630,7 +22633,7 @@
     </row>
     <row r="224" ht="15.0" customHeight="1">
       <c r="A224" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B224" s="15"/>
       <c r="C224" s="15"/>
@@ -22659,7 +22662,7 @@
     </row>
     <row r="225" ht="15.0" customHeight="1">
       <c r="A225" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B225" s="16">
         <v>162.77</v>
@@ -22730,7 +22733,7 @@
     </row>
     <row r="226" ht="15.0" customHeight="1">
       <c r="A226" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B226" s="22">
         <v>0.79</v>
@@ -22801,7 +22804,7 @@
     </row>
     <row r="227" ht="15.0" customHeight="1">
       <c r="A227" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B227" s="16">
         <v>163.57</v>
@@ -22872,7 +22875,7 @@
     </row>
     <row r="228" ht="15.0" customHeight="1">
       <c r="A228" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B228" s="22">
         <v>1.0</v>
@@ -22943,7 +22946,7 @@
     </row>
     <row r="229" ht="15.0" customHeight="1">
       <c r="A229" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B229" s="15"/>
       <c r="C229" s="15"/>
@@ -22974,7 +22977,7 @@
     </row>
     <row r="230" ht="15.0" customHeight="1">
       <c r="A230" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B230" s="15"/>
       <c r="C230" s="15"/>
@@ -23005,7 +23008,7 @@
     </row>
     <row r="231" ht="15.0" customHeight="1">
       <c r="A231" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B231" s="15"/>
       <c r="C231" s="15"/>
@@ -23824,7 +23827,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -24210,70 +24213,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -24349,7 +24352,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24447,7 +24450,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B20" s="16">
         <v>232.88</v>
@@ -24589,7 +24592,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B22" s="16">
         <v>285.54</v>
@@ -24656,7 +24659,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B23" s="21">
         <v>-11.7</v>
@@ -24798,7 +24801,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B25" s="21">
         <v>-38.62</v>
@@ -24869,7 +24872,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B26" s="22">
         <v>43.3</v>
@@ -24940,7 +24943,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="16">
@@ -25005,7 +25008,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B28" s="16">
         <v>248.09</v>
@@ -25038,7 +25041,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B29" s="20">
         <v>-1184.3</v>
@@ -25095,7 +25098,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B30" s="22">
         <v>12.87</v>
@@ -25142,7 +25145,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B31" s="20">
         <v>-289.05</v>
@@ -25213,7 +25216,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B32" s="20">
         <v>-369.8</v>
@@ -25284,7 +25287,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="22">
@@ -25349,7 +25352,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="21">
@@ -25392,7 +25395,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="22">
@@ -25457,7 +25460,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="21">
@@ -25553,7 +25556,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -25602,7 +25605,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -25637,7 +25640,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B40" s="21">
         <v>-2.34</v>
@@ -25686,7 +25689,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B41" s="19">
         <v>2326.47</v>
@@ -25757,7 +25760,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B42" s="20">
         <v>-457.57</v>
@@ -25828,7 +25831,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B43" s="21">
         <v>-15.21</v>
@@ -25899,7 +25902,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B44" s="22">
         <v>60.85</v>
@@ -25970,7 +25973,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B45" s="22">
         <v>11.7</v>
@@ -26027,7 +26030,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B46" s="21">
         <v>-2.34</v>
@@ -26096,7 +26099,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B47" s="22">
         <v>17.55</v>
@@ -26167,7 +26170,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -26226,7 +26229,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -26255,7 +26258,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -26316,7 +26319,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -26371,7 +26374,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -26424,7 +26427,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B53" s="22">
         <v>4.68</v>
@@ -26493,7 +26496,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -26538,7 +26541,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -26622,7 +26625,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -26651,7 +26654,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -26694,7 +26697,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -26723,7 +26726,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B60" s="25">
         <v>-380.33</v>
@@ -26794,7 +26797,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -26823,7 +26826,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -26872,7 +26875,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -26901,7 +26904,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -26930,7 +26933,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -26959,7 +26962,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -26990,7 +26993,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B67" s="21">
         <v>-46.81</v>
@@ -27029,7 +27032,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B68" s="22">
         <v>29.26</v>
@@ -27100,7 +27103,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B69" s="16">
         <v>1287.28</v>
@@ -27171,7 +27174,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B70" s="20">
         <v>-1976.56</v>
@@ -27242,7 +27245,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B71" s="20">
         <v>-363.95</v>
@@ -27285,7 +27288,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" s="20">
         <v>-140.43</v>
@@ -27322,7 +27325,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B73" s="20">
         <v>-744.28</v>
@@ -27393,7 +27396,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -27432,7 +27435,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -27471,7 +27474,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -27522,7 +27525,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15">
@@ -27563,7 +27566,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -27604,7 +27607,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -27643,7 +27646,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -27676,7 +27679,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B81" s="21">
         <v>-1.17</v>
@@ -27727,7 +27730,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B82" s="25">
         <v>-1956.67</v>
@@ -27798,7 +27801,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B83" s="21">
         <v>-9.36</v>
@@ -27851,7 +27854,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B84" s="15">
         <v>0.0</v>
@@ -27922,7 +27925,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B85" s="16">
         <v>242.19</v>
@@ -27993,7 +27996,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B86" s="16">
         <v>232.74</v>
@@ -28064,7 +28067,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B87" s="22">
         <v>1.17</v>
@@ -28105,7 +28108,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B88" s="26">
         <v>-9.36</v>
@@ -28176,7 +28179,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B89" s="16">
         <v>1868.9</v>
@@ -29145,7 +29148,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -29315,22 +29318,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -29765,7 +29768,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -29863,27 +29866,27 @@
         <v>70</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="30" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -29915,7 +29918,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B21" s="33">
         <v>21464.67</v>
@@ -29999,7 +30002,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B22" s="33">
         <v>27814.73</v>
@@ -30075,7 +30078,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
@@ -30107,7 +30110,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B24" s="33">
         <v>14762.21</v>
@@ -30191,7 +30194,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B25" s="33">
         <v>19939.58</v>
@@ -30267,7 +30270,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -30299,7 +30302,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="32" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B27" s="35">
         <v>90.25</v>
@@ -30383,7 +30386,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B28" s="34">
         <v>121.91</v>
@@ -30459,7 +30462,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -30491,7 +30494,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B30" s="36">
         <v>10.8</v>
@@ -30569,7 +30572,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B31" s="36">
         <v>6.99</v>
@@ -30637,7 +30640,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -30669,7 +30672,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B33" s="36">
         <v>4.82</v>
@@ -30749,7 +30752,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B34" s="36">
         <v>4.44</v>
@@ -30805,7 +30808,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B35" s="36">
         <v>4.82</v>
@@ -30889,7 +30892,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B36" s="36">
         <v>4.44</v>
@@ -30965,7 +30968,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -30997,7 +31000,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="32" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B38" s="35">
         <v>2.01</v>
@@ -31081,7 +31084,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="32" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B39" s="35">
         <v>2.51</v>
@@ -31157,7 +31160,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -31189,7 +31192,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B41" s="33"/>
       <c r="C41" s="33"/>
@@ -31239,7 +31242,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B42" s="33"/>
       <c r="C42" s="33"/>
@@ -31283,7 +31286,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -31315,7 +31318,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B44" s="35">
         <v>0.93</v>
@@ -31399,7 +31402,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="32" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B45" s="35">
         <v>1.33</v>
@@ -31475,7 +31478,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -31507,7 +31510,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="32" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B47" s="35">
         <v>9.26</v>
@@ -31583,7 +31586,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B48" s="35">
         <v>14.3</v>
@@ -31651,7 +31654,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
@@ -31683,7 +31686,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="32" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B50" s="35">
         <v>4.95</v>
@@ -31763,7 +31766,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="32" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B51" s="35">
         <v>5.75</v>
@@ -31839,7 +31842,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
@@ -31871,7 +31874,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="32" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B53" s="35">
         <v>40.56</v>
@@ -31947,7 +31950,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="32" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B54" s="35">
         <v>19.21</v>
@@ -32013,7 +32016,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
@@ -32045,7 +32048,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="32" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B56" s="35">
         <v>13.64</v>
@@ -32123,7 +32126,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="32" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B57" s="35">
         <v>2.51</v>
@@ -32199,7 +32202,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
@@ -32231,7 +32234,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="32" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B59" s="35">
         <v>0.05</v>
@@ -32307,7 +32310,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="32" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B60" s="38">
         <v>-1.44</v>
@@ -32365,7 +32368,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -32397,7 +32400,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="32" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B62" s="35">
         <v>1.36</v>
@@ -32481,7 +32484,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B63" s="35">
         <v>1.86</v>
@@ -32557,7 +32560,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -32589,7 +32592,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="32" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B65" s="35">
         <v>5.24</v>
@@ -32671,7 +32674,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="32" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B66" s="35">
         <v>7.63</v>
@@ -32747,7 +32750,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -32779,7 +32782,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="32" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B68" s="35">
         <v>10.54</v>
@@ -32863,7 +32866,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B69" s="35">
         <v>14.61</v>
@@ -32939,7 +32942,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="30" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -32971,7 +32974,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="32" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B71" s="35">
         <v>13.47</v>
@@ -33047,7 +33050,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="32" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B72" s="35">
         <v>19.99</v>
